--- a/frontend/public/templates/members-import-template.xlsx
+++ b/frontend/public/templates/members-import-template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +29,14 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,11 +45,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00F4EFFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008F73B5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +62,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -144,6 +149,63 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InsMembers" displayName="InsMembers" ref="A3:J5" headerRowCount="1">
+  <autoFilter ref="A3:J5"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Member ID"/>
+    <tableColumn id="2" name="First Name"/>
+    <tableColumn id="3" name="Surname"/>
+    <tableColumn id="4" name="Full Name"/>
+    <tableColumn id="5" name="Email"/>
+    <tableColumn id="6" name="Phone"/>
+    <tableColumn id="7" name="Join Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Organisation Name"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MembershipClub" displayName="MembershipClub" ref="A3:J5" headerRowCount="1">
+  <autoFilter ref="A3:J5"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Member ID"/>
+    <tableColumn id="2" name="First Name"/>
+    <tableColumn id="3" name="Surname"/>
+    <tableColumn id="4" name="Full Name"/>
+    <tableColumn id="5" name="Email"/>
+    <tableColumn id="6" name="Phone"/>
+    <tableColumn id="7" name="Join Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Organisation Name"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Society" displayName="Society" ref="A3:J5" headerRowCount="1">
+  <autoFilter ref="A3:J5"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Member ID"/>
+    <tableColumn id="2" name="First Name"/>
+    <tableColumn id="3" name="Surname"/>
+    <tableColumn id="4" name="Full Name"/>
+    <tableColumn id="5" name="Email"/>
+    <tableColumn id="6" name="Phone"/>
+    <tableColumn id="7" name="Join Date"/>
+    <tableColumn id="8" name="Status"/>
+    <tableColumn id="9" name="Organisation Name"/>
+    <tableColumn id="10" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,143 +497,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Member ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Branch/Group</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Ins Members import template</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>INS-001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Jane Dlamini</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>jane@example.com</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0825550101</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>Keep the sheet name unchanged. Required: Full Name or First Name + Surname, and Email or Member ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Join Date</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Organisation Name</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INS-1001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lerato</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mokoena</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lerato Mokoena</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lerato@example.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0821234567</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>POL-1001</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Pretoria West</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Imported insurance member example</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>INS-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Sipho Mokoena</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Insurance Members</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sample row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INS-1002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sipho</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dlamini</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sipho Dlamini</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>sipho@example.com</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0825550102</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0839876543</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>POL-1002</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Centurion</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Insurance Members</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -581,147 +696,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Member ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Branch/Group</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Membership Club import template</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CLUB-001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Lebo Ncube</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>lebo@example.com</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0825550201</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>Keep the sheet name unchanged. Required: Full Name or First Name + Surname, and Email or Member ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Join Date</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Organisation Name</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CLUB-2001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ayanda</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nkosi</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ayanda Nkosi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ayanda@example.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0842223344</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>CLUB-REF-01</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Gold Club</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Monthly member</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CLUB-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Ayanda Peters</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ayanda@example.com</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0825550202</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Expired</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>CLUB-REF-02</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Silver Club</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Needs renewal</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Membership Club</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sample row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CLUB-2002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Naledi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mabena</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Naledi Mabena</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>naledi@example.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0715556677</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Membership Club</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -731,146 +895,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Member ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Branch/Group</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Society import template</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SOC-001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Mpho Khumalo</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>mpho@example.com</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>0825550301</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+          <t>Keep the sheet name unchanged. Required: Full Name or First Name + Surname, and Email or Member ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Member ID</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Join Date</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Organisation Name</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SOC-3001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thabo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Khumalo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thabo Khumalo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thabo@example.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0721112233</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>SOC-REF-01</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Society North</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Committee member</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SOC-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Zanele Maseko</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>zanele@example.com</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>0825550302</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>SOC-REF-02</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Society East</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Awaiting documents</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Society</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sample row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SOC-3002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Neo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Peters</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Neo Peters</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>neo@example.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0764448899</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Society</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>